--- a/Results_greedy_improved.xlsx
+++ b/Results_greedy_improved.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -605,34 +605,34 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="F5" t="n">
-        <v>7.083333333333333</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G5" t="n">
-        <v>14.58333333333333</v>
+        <v>24.66666666666666</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>6.666666666666664</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>39.99999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -644,34 +644,34 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>8.333333333333334</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>7.777777777777778</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G6" t="n">
-        <v>16.11111111111111</v>
+        <v>26.11111111111111</v>
       </c>
       <c r="H6" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>6.111111111111114</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>55.00000000000003</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,28 +683,28 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>8.5</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="G7" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -725,13 +725,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>14.58333333333333</v>
+        <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>6.666666666666667</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>21.25</v>
+        <v>26</v>
       </c>
       <c r="H8" t="n">
         <v>31</v>
@@ -749,79 +749,79 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>16.11111111111111</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="F9" t="n">
-        <v>6.666666666666667</v>
+        <v>8.75</v>
       </c>
       <c r="G9" t="n">
-        <v>22.77777777777778</v>
+        <v>41.41666666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3.416666666666664</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>44.41666666666664</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>21.25</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>7.916666666666667</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>29.16666666666667</v>
+        <v>37</v>
       </c>
       <c r="H10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -836,19 +836,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>27.77777777777778</v>
+        <v>26.11111111111111</v>
       </c>
       <c r="F11" t="n">
         <v>7.222222222222222</v>
       </c>
       <c r="G11" t="n">
-        <v>35</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="H11" t="n">
         <v>36</v>
@@ -866,76 +866,76 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="F12" t="n">
-        <v>10.5</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G12" t="n">
-        <v>39.5</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="H12" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>16.44444444444444</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
-        <v>19.5</v>
+        <v>197.3333333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>33.16666666666667</v>
+        <v>37</v>
       </c>
       <c r="F13" t="n">
-        <v>4.583333333333333</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>37.75000000000001</v>
+        <v>43</v>
       </c>
       <c r="H13" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -949,46 +949,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>35</v>
+        <v>41.41666666666666</v>
       </c>
       <c r="F14" t="n">
-        <v>13.88888888888889</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>48.88888888888889</v>
+        <v>51.83333333333333</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8888888888888857</v>
+        <v>3.833333333333329</v>
       </c>
       <c r="J14" t="n">
         <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>12.4444444444444</v>
+        <v>53.6666666666666</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -998,22 +998,22 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>37.75000000000001</v>
+        <v>43</v>
       </c>
       <c r="F15" t="n">
-        <v>5.416666666666667</v>
+        <v>5.5</v>
       </c>
       <c r="G15" t="n">
-        <v>43.16666666666667</v>
+        <v>48.5</v>
       </c>
       <c r="H15" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1027,110 +1027,110 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>41.5</v>
+        <v>46.44444444444444</v>
       </c>
       <c r="F16" t="n">
-        <v>10.5</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>52</v>
+        <v>58.11111111111111</v>
       </c>
       <c r="H16" t="n">
         <v>53</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>5.111111111111107</v>
       </c>
       <c r="J16" t="n">
         <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>71.5555555555555</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>48.16666666666667</v>
+        <v>51.5</v>
       </c>
       <c r="F17" t="n">
-        <v>9.583333333333334</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>57.75000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="H17" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="I17" t="n">
-        <v>37.75000000000001</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
-        <v>339.7500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>49.88888888888889</v>
+        <v>51.83333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>13.33333333333333</v>
+        <v>6.25</v>
       </c>
       <c r="G18" t="n">
-        <v>63.22222222222222</v>
+        <v>58.08333333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1139,76 +1139,76 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>59.08333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>63</v>
+        <v>69.08333333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.083333333333329</v>
       </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>27.74999999999996</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>57.75000000000001</v>
+        <v>63.11111111111111</v>
       </c>
       <c r="F20" t="n">
-        <v>6.25</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G20" t="n">
-        <v>64</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1226,19 +1226,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>63</v>
+        <v>59.5</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>73</v>
+        <v>69.5</v>
       </c>
       <c r="H21" t="n">
         <v>74</v>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1271,13 +1271,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>63.22222222222222</v>
+        <v>69.08333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>11.66666666666667</v>
+        <v>8.75</v>
       </c>
       <c r="G22" t="n">
-        <v>74.88888888888889</v>
+        <v>77.83333333333333</v>
       </c>
       <c r="H22" t="n">
         <v>78</v>
@@ -1295,12 +1295,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1310,22 +1310,22 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>64</v>
+        <v>69.5</v>
       </c>
       <c r="F23" t="n">
-        <v>9.166666666666666</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>73.16666666666667</v>
+        <v>75.5</v>
       </c>
       <c r="H23" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1334,12 +1334,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1349,61 +1349,61 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G24" t="n">
-        <v>79</v>
+        <v>83.1111111111111</v>
       </c>
       <c r="H24" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>73.16666666666667</v>
+        <v>79.5</v>
       </c>
       <c r="F25" t="n">
-        <v>5.833333333333333</v>
+        <v>6.5</v>
       </c>
       <c r="G25" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H25" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1427,64 +1427,64 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>74.88888888888889</v>
+        <v>77.83333333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>9.444444444444445</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G26" t="n">
-        <v>84.33333333333333</v>
+        <v>84.91666666666666</v>
       </c>
       <c r="H26" t="n">
         <v>69</v>
       </c>
       <c r="I26" t="n">
-        <v>15.33333333333333</v>
+        <v>15.91666666666666</v>
       </c>
       <c r="J26" t="n">
         <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>107.3333333333333</v>
+        <v>111.4166666666666</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>81</v>
+        <v>84.1111111111111</v>
       </c>
       <c r="F27" t="n">
-        <v>9.583333333333334</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G27" t="n">
-        <v>90.58333333333333</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="H27" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="I27" t="n">
-        <v>8.583333333333329</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>51.49999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1495,23 +1495,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>79</v>
+        <v>88.91666666666666</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="G28" t="n">
-        <v>88</v>
+        <v>96.41666666666666</v>
       </c>
       <c r="H28" t="n">
         <v>104</v>
@@ -1529,40 +1529,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>84.33333333333333</v>
+        <v>86</v>
       </c>
       <c r="F29" t="n">
-        <v>10.55555555555556</v>
+        <v>11.5</v>
       </c>
       <c r="G29" t="n">
-        <v>94.88888888888889</v>
+        <v>97.5</v>
       </c>
       <c r="H29" t="n">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Results_greedy_improved.xlsx
+++ b/Results_greedy_improved.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O3</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7.2</v>
+        <v>6.25</v>
       </c>
       <c r="G2" t="n">
-        <v>7.2</v>
+        <v>6.25</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O1</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="G3" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,39 +554,1014 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.444444444444445</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9.444444444444445</v>
+      </c>
+      <c r="H4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ORD08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>38</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ORD11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>18</v>
+      </c>
+      <c r="H6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ORD09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9.444444444444445</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10.55555555555556</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="n">
+        <v>32</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ORD02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="G8" t="n">
+        <v>28</v>
+      </c>
+      <c r="H8" t="n">
+        <v>28</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ORD07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.833333333333333</v>
+      </c>
+      <c r="G9" t="n">
+        <v>27.83333333333333</v>
+      </c>
+      <c r="H9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ORD06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.888888888888889</v>
+      </c>
+      <c r="G10" t="n">
+        <v>28.88888888888889</v>
+      </c>
+      <c r="H10" t="n">
+        <v>31</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ORD25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>27.83333333333333</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="G11" t="n">
+        <v>36.58333333333333</v>
+      </c>
+      <c r="H11" t="n">
+        <v>53</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ORD14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>28</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ORD03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>28.88888888888889</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
+        <v>38.88888888888889</v>
+      </c>
+      <c r="H13" t="n">
+        <v>14</v>
+      </c>
+      <c r="I13" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="J13" t="n">
         <v>8</v>
       </c>
-      <c r="G4" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="K13" t="n">
+        <v>199.1111111111111</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ORD10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>36.58333333333333</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>41.58333333333333</v>
+      </c>
+      <c r="H14" t="n">
+        <v>43</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ORD16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>38.88888888888889</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8.888888888888889</v>
+      </c>
+      <c r="G15" t="n">
+        <v>47.77777777777777</v>
+      </c>
+      <c r="H15" t="n">
+        <v>63</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ORD12</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>18</v>
+      </c>
+      <c r="I16" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ORD13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>41.58333333333333</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.583333333333333</v>
+      </c>
+      <c r="G17" t="n">
+        <v>46.16666666666666</v>
+      </c>
+      <c r="H17" t="n">
+        <v>49</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>11</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ORD27</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>49.16666666666666</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>54.16666666666666</v>
+      </c>
+      <c r="H18" t="n">
+        <v>78</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ORD19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>47.77777777777777</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="G19" t="n">
+        <v>58.88888888888889</v>
+      </c>
+      <c r="H19" t="n">
+        <v>74</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>15</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ORD15</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G20" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>66</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ORD20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="n">
+        <v>64.16666666666666</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="G21" t="n">
+        <v>70.41666666666666</v>
+      </c>
+      <c r="H21" t="n">
+        <v>70</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.4166666666666572</v>
+      </c>
+      <c r="J21" t="n">
+        <v>12</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.999999999999886</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ORD28</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>62.88888888888889</v>
+      </c>
+      <c r="F22" t="n">
+        <v>12.77777777777778</v>
+      </c>
+      <c r="G22" t="n">
+        <v>75.66666666666666</v>
+      </c>
+      <c r="H22" t="n">
+        <v>82</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ORD21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>73</v>
+      </c>
+      <c r="H23" t="n">
+        <v>69</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" t="n">
         <v>28</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ORD26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>70.41666666666666</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9.166666666666666</v>
+      </c>
+      <c r="G24" t="n">
+        <v>79.58333333333333</v>
+      </c>
+      <c r="H24" t="n">
+        <v>81</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>11</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ORD18</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>73</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>78</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>10</v>
+      </c>
+      <c r="K25" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ORD22</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>75.66666666666666</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7.222222222222222</v>
+      </c>
+      <c r="G26" t="n">
+        <v>82.88888888888889</v>
+      </c>
+      <c r="H26" t="n">
+        <v>86</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>10</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ORD17</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>79.58333333333333</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.833333333333333</v>
+      </c>
+      <c r="G27" t="n">
+        <v>85.41666666666666</v>
+      </c>
+      <c r="H27" t="n">
+        <v>85</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4166666666666572</v>
+      </c>
+      <c r="J27" t="n">
         <v>12</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K27" t="n">
+        <v>4.999999999999886</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ORD23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>85.88888888888889</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" t="n">
+        <v>95.88888888888889</v>
+      </c>
+      <c r="H28" t="n">
+        <v>104</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>9</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ORD24</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>93</v>
+      </c>
+      <c r="H29" t="n">
+        <v>113</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>12</v>
+      </c>
+      <c r="K29" t="n">
         <v>0</v>
       </c>
     </row>
